--- a/Pairs Medals Wiki.xlsx
+++ b/Pairs Medals Wiki.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulinareina/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulinareina/Desktop/Career Exploration Stuff/Data Science Training/The Data Incubator/The Data Incubator Onboarding/Streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EE7CC3C-05C2-7947-A45D-E42DCED42FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926AF159-C178-F84E-B118-32597AEF94E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16300" xr2:uid="{DA0473D0-3A83-9F40-9B7C-0E04812C00DB}"/>
+    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16300" xr2:uid="{DA0473D0-3A83-9F40-9B7C-0E04812C00DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="163">
   <si>
     <t>Games</t>
   </si>
@@ -3483,6 +3482,27 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>2026 Milano Cortina</t>
+  </si>
+  <si>
+    <t>Riku Miura</t>
+  </si>
+  <si>
+    <t>and Riuchi Kihara (JAP)</t>
+  </si>
+  <si>
+    <t>Anastasiia Metelkina</t>
+  </si>
+  <si>
+    <t>and Luka Berulava (GE0)</t>
+  </si>
+  <si>
+    <t>Minerva Fabienne Hase</t>
+  </si>
+  <si>
+    <t>and Nikita Volodin (GER)</t>
   </si>
 </sst>
 </file>
@@ -8648,8 +8668,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C3F9900-6C49-5D42-B3D3-DF02BC38C396}">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="4" width="36.83203125" customWidth="1"/>
+    <col min="5" max="7" width="26.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -9429,6 +9453,34 @@
       </c>
       <c r="D58" s="3" t="s">
         <v>155</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
